--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156406</v>
+        <v>123156411</v>
       </c>
       <c r="B2" t="n">
-        <v>109041</v>
+        <v>44690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491320</v>
+        <v>491218</v>
       </c>
       <c r="R2" t="n">
-        <v>6444595</v>
+        <v>6444285</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156411</v>
+        <v>123156406</v>
       </c>
       <c r="B3" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491218</v>
+        <v>491320</v>
       </c>
       <c r="R3" t="n">
-        <v>6444285</v>
+        <v>6444595</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,10 +894,121 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123178330</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109041</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trehörna, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491225</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6444303</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trehörna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, hela vägområdet</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Melina Eberhagen</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156411</v>
+        <v>123178330</v>
       </c>
       <c r="B2" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491218</v>
+        <v>491225</v>
       </c>
       <c r="R2" t="n">
-        <v>6444285</v>
+        <v>6444303</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178330</v>
+        <v>123156411</v>
       </c>
       <c r="B4" t="n">
-        <v>109041</v>
+        <v>44690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +917,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491225</v>
+        <v>491218</v>
       </c>
       <c r="R4" t="n">
-        <v>6444303</v>
+        <v>6444285</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178330</v>
+        <v>123156411</v>
       </c>
       <c r="B2" t="n">
-        <v>109041</v>
+        <v>44690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491225</v>
+        <v>491218</v>
       </c>
       <c r="R2" t="n">
-        <v>6444303</v>
+        <v>6444285</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156411</v>
+        <v>123178330</v>
       </c>
       <c r="B4" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491218</v>
+        <v>491225</v>
       </c>
       <c r="R4" t="n">
-        <v>6444285</v>
+        <v>6444303</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156411</v>
+        <v>123178330</v>
       </c>
       <c r="B2" t="n">
-        <v>44690</v>
+        <v>109041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491218</v>
+        <v>491225</v>
       </c>
       <c r="R2" t="n">
-        <v>6444285</v>
+        <v>6444303</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156406</v>
+        <v>123156411</v>
       </c>
       <c r="B3" t="n">
-        <v>109041</v>
+        <v>44690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491320</v>
+        <v>491218</v>
       </c>
       <c r="R3" t="n">
-        <v>6444595</v>
+        <v>6444285</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178330</v>
+        <v>123156406</v>
       </c>
       <c r="B4" t="n">
         <v>109041</v>
@@ -938,17 +934,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491225</v>
+        <v>491320</v>
       </c>
       <c r="R4" t="n">
-        <v>6444303</v>
+        <v>6444595</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123178330</v>
       </c>
       <c r="B2" t="n">
-        <v>109041</v>
+        <v>109045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123156411</v>
       </c>
       <c r="B3" t="n">
-        <v>44690</v>
+        <v>44693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>123156406</v>
       </c>
       <c r="B4" t="n">
-        <v>109041</v>
+        <v>109045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123178330</v>
       </c>
       <c r="B2" t="n">
-        <v>109045</v>
+        <v>109047</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156411</v>
+        <v>123156406</v>
       </c>
       <c r="B3" t="n">
-        <v>44693</v>
+        <v>109047</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491218</v>
+        <v>491320</v>
       </c>
       <c r="R3" t="n">
-        <v>6444285</v>
+        <v>6444595</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156406</v>
+        <v>123156411</v>
       </c>
       <c r="B4" t="n">
-        <v>109045</v>
+        <v>44693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491320</v>
+        <v>491218</v>
       </c>
       <c r="R4" t="n">
-        <v>6444595</v>
+        <v>6444285</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178330</v>
+        <v>123156406</v>
       </c>
       <c r="B2" t="n">
-        <v>109047</v>
+        <v>109053</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,17 +708,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491225</v>
+        <v>491320</v>
       </c>
       <c r="R2" t="n">
-        <v>6444303</v>
+        <v>6444595</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156406</v>
+        <v>123178330</v>
       </c>
       <c r="B3" t="n">
-        <v>109047</v>
+        <v>109053</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +823,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491320</v>
+        <v>491225</v>
       </c>
       <c r="R3" t="n">
-        <v>6444595</v>
+        <v>6444303</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156406</v>
       </c>
       <c r="B2" t="n">
-        <v>109056</v>
+        <v>109073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>123156411</v>
       </c>
       <c r="B3" t="n">
-        <v>44693</v>
+        <v>44699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>123178330</v>
       </c>
       <c r="B4" t="n">
-        <v>109056</v>
+        <v>109073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156406</v>
+        <v>123178330</v>
       </c>
       <c r="B2" t="n">
-        <v>109073</v>
+        <v>109091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,21 +708,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491320</v>
+        <v>491225</v>
       </c>
       <c r="R2" t="n">
-        <v>6444595</v>
+        <v>6444303</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156411</v>
+        <v>123156406</v>
       </c>
       <c r="B3" t="n">
-        <v>44699</v>
+        <v>109091</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491218</v>
+        <v>491320</v>
       </c>
       <c r="R3" t="n">
-        <v>6444285</v>
+        <v>6444595</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178330</v>
+        <v>123156411</v>
       </c>
       <c r="B4" t="n">
-        <v>109073</v>
+        <v>44702</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +917,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491225</v>
+        <v>491218</v>
       </c>
       <c r="R4" t="n">
-        <v>6444303</v>
+        <v>6444285</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178330</v>
+        <v>123156406</v>
       </c>
       <c r="B2" t="n">
-        <v>109091</v>
+        <v>109093</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,17 +708,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491225</v>
+        <v>491320</v>
       </c>
       <c r="R2" t="n">
-        <v>6444303</v>
+        <v>6444595</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156406</v>
+        <v>123178330</v>
       </c>
       <c r="B3" t="n">
-        <v>109091</v>
+        <v>109093</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +823,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491320</v>
+        <v>491225</v>
       </c>
       <c r="R3" t="n">
-        <v>6444595</v>
+        <v>6444303</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5187-2024 artfynd.xlsx
+++ b/artfynd/A 5187-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156406</v>
       </c>
       <c r="B2" t="n">
-        <v>109093</v>
+        <v>108668</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178330</v>
+        <v>123156411</v>
       </c>
       <c r="B3" t="n">
-        <v>109093</v>
+        <v>44702</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>102020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491225</v>
+        <v>491218</v>
       </c>
       <c r="R3" t="n">
-        <v>6444303</v>
+        <v>6444285</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, hela vägområdet</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156411</v>
+        <v>123178330</v>
       </c>
       <c r="B4" t="n">
-        <v>44702</v>
+        <v>108668</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102020</v>
+        <v>220228</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trehörna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491218</v>
+        <v>491225</v>
       </c>
       <c r="R4" t="n">
-        <v>6444285</v>
+        <v>6444303</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, hela vägområdet</t>
         </is>
       </c>
       <c r="AD4" t="b">
